--- a/data/trans_camb/P1803_2016_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1803_2016_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,61</t>
+          <t>-1,68; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,48</t>
+          <t>0,58; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,11</t>
+          <t>0,16; 3,07</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 95,36</t>
+          <t>-37,39; 93,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 142,12</t>
+          <t>10,63; 143,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 94,78</t>
+          <t>3,24; 91,98</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,65</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 39,91</t>
+          <t>1,87; 4,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,83</t>
+          <t>2,64; 5,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 25,11</t>
+          <t>2,68; 4,91</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>320,65%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177,78%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,55; 941,44</t>
+          <t>37,92; 134,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 108,65</t>
+          <t>41,67; 118,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,01; 537,33</t>
+          <t>50,72; 115,48</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>5,76</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,3</t>
+          <t>1,56; 8,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 10,9</t>
+          <t>3,05; 9,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,1</t>
+          <t>3,38; 8,37</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,93; 175,35</t>
+          <t>16,08; 163,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,45; 154,46</t>
+          <t>26,78; 140,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,93; 142,13</t>
+          <t>37,35; 131,11</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>3,93</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,55</t>
+          <t>2,33; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,28</t>
+          <t>3,31; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 18,16</t>
+          <t>3,01; 4,77</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>225,96%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139,29%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,92; 674,72</t>
+          <t>45,93; 116,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,19; 103,99</t>
+          <t>54,03; 114,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70,44; 360,12</t>
+          <t>55,48; 101,62</t>
         </is>
       </c>
     </row>
